--- a/artfynd/A 44847-2023 artfynd.xlsx
+++ b/artfynd/A 44847-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44847-2023 artfynd.xlsx
+++ b/artfynd/A 44847-2023 artfynd.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">

--- a/artfynd/A 44847-2023 artfynd.xlsx
+++ b/artfynd/A 44847-2023 artfynd.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">

--- a/artfynd/A 44847-2023 artfynd.xlsx
+++ b/artfynd/A 44847-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76871344</v>
+        <v>76871335</v>
       </c>
       <c r="B2" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R2" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En gammal du gmärkt med svart och röd ring. Möjligen siffran 7 i den röda</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,32 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76871335</v>
+        <v>76871330</v>
       </c>
       <c r="B3" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102935</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ejder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Somateria mollissima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R3" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En gammal du gmärkt med svart och röd ring. Möjligen siffran 7 i den röda</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76871337</v>
+        <v>76871336</v>
       </c>
       <c r="B4" t="n">
-        <v>55946</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,26 +919,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102963</v>
+        <v>102950</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -965,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R4" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,15 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76871336</v>
+        <v>76871337</v>
       </c>
       <c r="B5" t="n">
-        <v>55786</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,26 +1033,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102950</v>
+        <v>102963</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strandskata</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haematopus ostralegus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1084,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R5" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,12 +1139,7 @@
         <v>76871340</v>
       </c>
       <c r="B6" t="n">
-        <v>55978</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R6" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1275,32 +1250,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>76871338</v>
+        <v>76871339</v>
       </c>
       <c r="B7" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102964</v>
+        <v>102967</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Havstrut</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Larus marinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1310,7 +1280,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1322,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R7" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,32 +1364,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>76871342</v>
+        <v>76871344</v>
       </c>
       <c r="B8" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205976</v>
+        <v>103037</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1429,7 +1394,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1441,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R8" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1486,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,42 +1478,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>76871339</v>
+        <v>76871348</v>
       </c>
       <c r="B9" t="n">
-        <v>55993</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102967</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstrut</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Larus marinus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1560,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R9" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1595,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1605,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,42 +1592,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76871330</v>
+        <v>76871342</v>
       </c>
       <c r="B10" t="n">
-        <v>55557</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102935</v>
+        <v>205976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ejder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Somateria mollissima</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1679,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707959.2470098112</v>
+        <v>707959</v>
       </c>
       <c r="R10" t="n">
-        <v>6674806.551945467</v>
+        <v>6674807</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1714,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1724,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,15 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88726016</v>
+        <v>88726010</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707780.9233450036</v>
+        <v>707781</v>
       </c>
       <c r="R11" t="n">
-        <v>6675033.901884181</v>
+        <v>6675034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,19 +1777,9 @@
           <t>2020-10-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-10-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,12 +1814,7 @@
         <v>88726047</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707779.6021091619</v>
+        <v>707780</v>
       </c>
       <c r="R12" t="n">
-        <v>6674977.951353024</v>
+        <v>6674978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,19 +1883,9 @@
           <t>2020-10-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44847-2023 artfynd.xlsx
+++ b/artfynd/A 44847-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871335</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871330</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871336</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871337</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871340</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871339</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871344</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,6 +1629,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871348</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1703,6 +1748,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76871342</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88726010</t>
         </is>
       </c>
     </row>
@@ -1914,8 +1969,26 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88726047</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>